--- a/ZonasEscolares/excels/JUNIN-HUANCAYO-HUANCAYO.xlsx
+++ b/ZonasEscolares/excels/JUNIN-HUANCAYO-HUANCAYO.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2566,7 +2566,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2774,7 +2774,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3034,7 +3034,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3190,7 +3190,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3242,7 +3242,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3294,7 +3294,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3346,7 +3346,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3450,7 +3450,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3554,7 +3554,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3606,7 +3606,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3658,7 +3658,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3710,7 +3710,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3762,7 +3762,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3918,7 +3918,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4126,7 +4126,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4282,7 +4282,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4386,7 +4386,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4438,7 +4438,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4542,7 +4542,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4594,7 +4594,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4698,7 +4698,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4750,7 +4750,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/JUNIN-HUANCAYO-HUANCAYO.xlsx
+++ b/ZonasEscolares/excels/JUNIN-HUANCAYO-HUANCAYO.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>253</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-12.07044</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-75.21324</v>
-      </c>
-      <c r="I2" t="n">
-        <v>292</v>
-      </c>
-      <c r="J2" t="n">
-        <v>13</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-12.07044</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-75.21324</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>292</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>254 OLIMPIA SANCHEZ MORENO</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-12.06</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-75.203</v>
-      </c>
-      <c r="I3" t="n">
-        <v>391</v>
-      </c>
-      <c r="J3" t="n">
-        <v>16</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-12.06</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-75.203</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>391</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>300</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-12.073669</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-75.19998099999999</v>
-      </c>
-      <c r="I4" t="n">
-        <v>481</v>
-      </c>
-      <c r="J4" t="n">
-        <v>20</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-12.073669</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-75.199981</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>481</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>30320 JESUS EL NAZARENO</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-12.0736</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-75.22410000000001</v>
-      </c>
-      <c r="I5" t="n">
-        <v>476</v>
-      </c>
-      <c r="J5" t="n">
-        <v>26</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-12.0736</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-75.2241</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>476</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>DANIEL ALCIDES CARRION</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-12.07986</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-75.22490999999999</v>
-      </c>
-      <c r="I6" t="n">
-        <v>260</v>
-      </c>
-      <c r="J6" t="n">
-        <v>14</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-12.07986</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-75.22491</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>372</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-12.0506</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-75.199</v>
-      </c>
-      <c r="I7" t="n">
-        <v>263</v>
-      </c>
-      <c r="J7" t="n">
-        <v>17</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-12.0506</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-75.199</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>465</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-12.0713</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-75.20480000000001</v>
-      </c>
-      <c r="I8" t="n">
-        <v>280</v>
-      </c>
-      <c r="J8" t="n">
-        <v>14</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-12.0713</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-75.2048</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>30001 SANTA ROSA DE LIMA</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-12.0544</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-75.18859999999999</v>
-      </c>
-      <c r="I9" t="n">
-        <v>322</v>
-      </c>
-      <c r="J9" t="n">
-        <v>14</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-12.0544</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-75.1886</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>30003 PEDRO R. DIAZ HUAMAN</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-12.02444</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-75.18406</v>
-      </c>
-      <c r="I10" t="n">
-        <v>238</v>
-      </c>
-      <c r="J10" t="n">
-        <v>12</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-12.02444</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-75.18406</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>30005 SAN FRANCISCO DE ASIS / 30005 SAN FRANSISCO DE ASIS</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-12.0338</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-75.1909</v>
-      </c>
-      <c r="I11" t="n">
-        <v>426</v>
-      </c>
-      <c r="J11" t="n">
-        <v>18</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-12.0338</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-75.1909</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>426</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>30009 VIRGEN DE GUADALUPE</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-12.043</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-75.19459999999999</v>
-      </c>
-      <c r="I12" t="n">
-        <v>566</v>
-      </c>
-      <c r="J12" t="n">
-        <v>34</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-12.043</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-75.1946</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>566</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>30011 VIRGEN DEL CARMEN</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-12.06016</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-75.194</v>
-      </c>
-      <c r="I13" t="n">
-        <v>372</v>
-      </c>
-      <c r="J13" t="n">
-        <v>24</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-12.06016</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-75.194</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>30054 SANTA MARIA REYNA</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-12.070532</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-75.211277</v>
-      </c>
-      <c r="I14" t="n">
-        <v>858</v>
-      </c>
-      <c r="J14" t="n">
-        <v>37</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-12.070532</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-75.211277</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>858</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>MARIA INMACULADA</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-12.06567</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-75.20904</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1672</v>
-      </c>
-      <c r="J15" t="n">
-        <v>121</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-12.06567</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-75.20904</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1672</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>30057 / 30057 MARIA DE FATIMA</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-12.0761</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-75.2133</v>
-      </c>
-      <c r="I16" t="n">
-        <v>576</v>
-      </c>
-      <c r="J16" t="n">
-        <v>26</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-12.0761</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-75.2133</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>576</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>30059 ROSA DE AMERICA</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-12.06955</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-75.21344999999999</v>
-      </c>
-      <c r="I17" t="n">
-        <v>1246</v>
-      </c>
-      <c r="J17" t="n">
-        <v>49</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-12.06955</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-75.21345</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1246</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>30124 SAN FRANCISCO DE ASIS</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-12.06633</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-75.19819</v>
-      </c>
-      <c r="I18" t="n">
-        <v>268</v>
-      </c>
-      <c r="J18" t="n">
-        <v>16</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-12.06633</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-75.19819</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>30128</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-12.0577</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-75.18715</v>
-      </c>
-      <c r="I19" t="n">
-        <v>337</v>
-      </c>
-      <c r="J19" t="n">
-        <v>18</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-12.0577</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-75.18715</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>337</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1457,20 +1625,30 @@
           <t>31458 SAN JUDAS TADEO</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-12.0676</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-75.19370000000001</v>
-      </c>
-      <c r="I20" t="n">
-        <v>204</v>
-      </c>
-      <c r="J20" t="n">
-        <v>15</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-12.0676</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-75.1937</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1509,20 +1687,30 @@
           <t>31506 SAGRADO CORAZON DE JESUS</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-12.07186</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-75.21074</v>
-      </c>
-      <c r="I21" t="n">
-        <v>644</v>
-      </c>
-      <c r="J21" t="n">
-        <v>35</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-12.07186</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-75.21074</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1561,20 +1749,30 @@
           <t>31507 DOMINGO F. SARMIENTO</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-12.06955</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-75.20631</v>
-      </c>
-      <c r="I22" t="n">
-        <v>744</v>
-      </c>
-      <c r="J22" t="n">
-        <v>36</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-12.06955</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-75.20631</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>744</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1613,20 +1811,30 @@
           <t>31540 SANTA ISABEL</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>-12.05764</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-75.20274999999999</v>
-      </c>
-      <c r="I23" t="n">
-        <v>1518</v>
-      </c>
-      <c r="J23" t="n">
-        <v>59</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-12.05764</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-75.20275</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1518</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1665,20 +1873,30 @@
           <t>31541 EMMA LUZMILA CALLE VERGARA</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>-12.06587</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-75.20936</v>
-      </c>
-      <c r="I24" t="n">
-        <v>1028</v>
-      </c>
-      <c r="J24" t="n">
-        <v>49</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-12.06587</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-75.20936</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1028</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1717,20 +1935,30 @@
           <t>31542 VIRGEN MARIA ADMIRABLE</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>-12.073551</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-75.199432</v>
-      </c>
-      <c r="I25" t="n">
-        <v>1091</v>
-      </c>
-      <c r="J25" t="n">
-        <v>54</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-12.073551</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-75.199432</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1091</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1769,20 +1997,30 @@
           <t>31554 JOSE C. MARIATEGUI</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>-12.07723</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-75.20809</v>
-      </c>
-      <c r="I26" t="n">
-        <v>894</v>
-      </c>
-      <c r="J26" t="n">
-        <v>53</v>
-      </c>
-      <c r="K26" t="n">
-        <v>1</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-12.07723</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-75.20809</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>894</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1821,20 +2059,30 @@
           <t>VIRGEN DE FATIMA</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>-12.05792</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-75.19586</v>
-      </c>
-      <c r="I27" t="n">
-        <v>718</v>
-      </c>
-      <c r="J27" t="n">
-        <v>50</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-12.05792</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-75.19586</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>718</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1873,20 +2121,30 @@
           <t>PILOTO SANTA ISABEL</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>-12.05843</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-75.20263</v>
-      </c>
-      <c r="I28" t="n">
-        <v>3648</v>
-      </c>
-      <c r="J28" t="n">
-        <v>209</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-12.05843</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-75.20263</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>3648</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1925,20 +2183,30 @@
           <t>NUESTRA SEÑORA DE COCHARCAS</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>-12.07517</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-75.20169</v>
-      </c>
-      <c r="I29" t="n">
-        <v>2143</v>
-      </c>
-      <c r="J29" t="n">
-        <v>114</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-12.07517</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-75.20169</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2143</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1977,20 +2245,30 @@
           <t>SAN FRANCISCO DE ASIS</t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>-12.06401</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-75.18805</v>
-      </c>
-      <c r="I30" t="n">
-        <v>262</v>
-      </c>
-      <c r="J30" t="n">
-        <v>18</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-12.06401</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-75.18805</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2029,20 +2307,30 @@
           <t>LOS ANDES</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>-12.02506</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-75.18379</v>
-      </c>
-      <c r="I31" t="n">
-        <v>253</v>
-      </c>
-      <c r="J31" t="n">
-        <v>21</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-12.02506</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-75.18379</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2081,20 +2369,30 @@
           <t>NUESTRA SEÑORA DEL ROSARIO</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>-12.06998</v>
-      </c>
-      <c r="H32" t="n">
-        <v>-75.21226</v>
-      </c>
-      <c r="I32" t="n">
-        <v>2007</v>
-      </c>
-      <c r="J32" t="n">
-        <v>98</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-12.06998</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-75.21226</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2133,20 +2431,30 @@
           <t>SANTA MARIA REYNA</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>-12.07529</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-75.22055</v>
-      </c>
-      <c r="I33" t="n">
-        <v>731</v>
-      </c>
-      <c r="J33" t="n">
-        <v>46</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-12.07529</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-75.22055</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>731</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2185,20 +2493,30 @@
           <t>31363 LA ASUNCION / 406 LA ASUNCION / LA ASUNCION</t>
         </is>
       </c>
-      <c r="G34" t="n">
-        <v>-12.029846</v>
-      </c>
-      <c r="H34" t="n">
-        <v>-75.190427</v>
-      </c>
-      <c r="I34" t="n">
-        <v>1075</v>
-      </c>
-      <c r="J34" t="n">
-        <v>54</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-12.029846</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>-75.190427</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1075</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2237,20 +2555,30 @@
           <t>CLARETIANO</t>
         </is>
       </c>
-      <c r="G35" t="n">
-        <v>-12.06242</v>
-      </c>
-      <c r="H35" t="n">
-        <v>-75.20534000000001</v>
-      </c>
-      <c r="I35" t="n">
-        <v>981</v>
-      </c>
-      <c r="J35" t="n">
-        <v>57</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-12.06242</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-75.20534</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>981</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2289,20 +2617,30 @@
           <t>ANDINO</t>
         </is>
       </c>
-      <c r="G36" t="n">
-        <v>-12.06371</v>
-      </c>
-      <c r="H36" t="n">
-        <v>-75.20650000000001</v>
-      </c>
-      <c r="I36" t="n">
-        <v>795</v>
-      </c>
-      <c r="J36" t="n">
-        <v>61</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-12.06371</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>-75.2065</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>795</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2341,20 +2679,30 @@
           <t>GOTITAS DE ROCIO</t>
         </is>
       </c>
-      <c r="G37" t="n">
-        <v>-12.05834</v>
-      </c>
-      <c r="H37" t="n">
-        <v>-75.2067</v>
-      </c>
-      <c r="I37" t="n">
-        <v>295</v>
-      </c>
-      <c r="J37" t="n">
-        <v>18</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-12.05834</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>-75.2067</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>295</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2393,20 +2741,30 @@
           <t>ROSA DE SANTA MARIA</t>
         </is>
       </c>
-      <c r="G38" t="n">
-        <v>-12.073214</v>
-      </c>
-      <c r="H38" t="n">
-        <v>-75.19807400000001</v>
-      </c>
-      <c r="I38" t="n">
-        <v>99</v>
-      </c>
-      <c r="J38" t="n">
-        <v>4</v>
-      </c>
-      <c r="K38" t="n">
-        <v>1</v>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-12.073214</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>-75.198074</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2445,20 +2803,30 @@
           <t>COLEGIO ADVENTISTA HUANCAYO</t>
         </is>
       </c>
-      <c r="G39" t="n">
-        <v>-12.07209</v>
-      </c>
-      <c r="H39" t="n">
-        <v>-75.21168</v>
-      </c>
-      <c r="I39" t="n">
-        <v>328</v>
-      </c>
-      <c r="J39" t="n">
-        <v>21</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-12.07209</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>-75.21168</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2497,20 +2865,30 @@
           <t>RAMIRO VILLAVERDE LAZO</t>
         </is>
       </c>
-      <c r="G40" t="n">
-        <v>-12.05737</v>
-      </c>
-      <c r="H40" t="n">
-        <v>-75.19264</v>
-      </c>
-      <c r="I40" t="n">
-        <v>933</v>
-      </c>
-      <c r="J40" t="n">
-        <v>60</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-12.05737</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>-75.19264</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>933</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2549,20 +2927,30 @@
           <t>SAN JUAN BOSCO</t>
         </is>
       </c>
-      <c r="G41" t="n">
-        <v>-12.06867</v>
-      </c>
-      <c r="H41" t="n">
-        <v>-75.2136</v>
-      </c>
-      <c r="I41" t="n">
-        <v>348</v>
-      </c>
-      <c r="J41" t="n">
-        <v>14</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-12.06867</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>-75.2136</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>348</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2601,20 +2989,30 @@
           <t>ZARATE</t>
         </is>
       </c>
-      <c r="G42" t="n">
-        <v>-12.06021</v>
-      </c>
-      <c r="H42" t="n">
-        <v>-75.20687</v>
-      </c>
-      <c r="I42" t="n">
-        <v>1356</v>
-      </c>
-      <c r="J42" t="n">
-        <v>50</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-12.06021</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>-75.20687</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1356</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -2653,20 +3051,30 @@
           <t>SAN CARLOS</t>
         </is>
       </c>
-      <c r="G43" t="n">
-        <v>-12.05908</v>
-      </c>
-      <c r="H43" t="n">
-        <v>-75.20614999999999</v>
-      </c>
-      <c r="I43" t="n">
-        <v>250</v>
-      </c>
-      <c r="J43" t="n">
-        <v>17</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-12.05908</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>-75.20615</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -2705,20 +3113,30 @@
           <t>30209</t>
         </is>
       </c>
-      <c r="G44" t="n">
-        <v>-12.02922</v>
-      </c>
-      <c r="H44" t="n">
-        <v>-75.22824</v>
-      </c>
-      <c r="I44" t="n">
-        <v>802</v>
-      </c>
-      <c r="J44" t="n">
-        <v>39</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-12.02922</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>-75.22824</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>802</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -2757,20 +3175,30 @@
           <t>31509 / 31509 RICARDO MENENDEZ MENENDEZ</t>
         </is>
       </c>
-      <c r="G45" t="n">
-        <v>-12.0597</v>
-      </c>
-      <c r="H45" t="n">
-        <v>-75.2178</v>
-      </c>
-      <c r="I45" t="n">
-        <v>1144</v>
-      </c>
-      <c r="J45" t="n">
-        <v>56</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>-12.0597</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>-75.2178</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1144</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -2809,20 +3237,30 @@
           <t>31595 / 31595 FLORENCIO V. HINOSTROZA C.</t>
         </is>
       </c>
-      <c r="G46" t="n">
-        <v>-12.0253</v>
-      </c>
-      <c r="H46" t="n">
-        <v>-75.23659000000001</v>
-      </c>
-      <c r="I46" t="n">
-        <v>551</v>
-      </c>
-      <c r="J46" t="n">
-        <v>26</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-12.0253</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>-75.23659</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>551</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -2861,20 +3299,30 @@
           <t>MARISCAL CASTILLA</t>
         </is>
       </c>
-      <c r="G47" t="n">
-        <v>-12.05916</v>
-      </c>
-      <c r="H47" t="n">
-        <v>-75.21802</v>
-      </c>
-      <c r="I47" t="n">
-        <v>2302</v>
-      </c>
-      <c r="J47" t="n">
-        <v>85</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0</v>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-12.05916</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>-75.21802</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2302</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -2913,20 +3361,30 @@
           <t>30227</t>
         </is>
       </c>
-      <c r="G48" t="n">
-        <v>-11.97212</v>
-      </c>
-      <c r="H48" t="n">
-        <v>-75.25221000000001</v>
-      </c>
-      <c r="I48" t="n">
-        <v>293</v>
-      </c>
-      <c r="J48" t="n">
-        <v>14</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0</v>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>-11.97212</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>-75.25221</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>293</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -2965,20 +3423,30 @@
           <t>JOSE OLAYA</t>
         </is>
       </c>
-      <c r="G49" t="n">
-        <v>-11.9746</v>
-      </c>
-      <c r="H49" t="n">
-        <v>-75.2568</v>
-      </c>
-      <c r="I49" t="n">
-        <v>320</v>
-      </c>
-      <c r="J49" t="n">
-        <v>24</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0</v>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>-11.9746</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>-75.2568</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -3017,20 +3485,30 @@
           <t>30172</t>
         </is>
       </c>
-      <c r="G50" t="n">
-        <v>-12.11</v>
-      </c>
-      <c r="H50" t="n">
-        <v>-75.2021</v>
-      </c>
-      <c r="I50" t="n">
-        <v>535</v>
-      </c>
-      <c r="J50" t="n">
-        <v>25</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0</v>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>-12.11</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>-75.2021</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>535</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -3069,20 +3547,30 @@
           <t>30173</t>
         </is>
       </c>
-      <c r="G51" t="n">
-        <v>-12.136861</v>
-      </c>
-      <c r="H51" t="n">
-        <v>-75.222522</v>
-      </c>
-      <c r="I51" t="n">
-        <v>895</v>
-      </c>
-      <c r="J51" t="n">
-        <v>36</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0</v>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>-12.136861</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>-75.222522</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>895</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -3121,20 +3609,30 @@
           <t>30175</t>
         </is>
       </c>
-      <c r="G52" t="n">
-        <v>-12.12248</v>
-      </c>
-      <c r="H52" t="n">
-        <v>-75.21541999999999</v>
-      </c>
-      <c r="I52" t="n">
-        <v>288</v>
-      </c>
-      <c r="J52" t="n">
-        <v>16</v>
-      </c>
-      <c r="K52" t="n">
-        <v>0</v>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>-12.12248</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>-75.21542</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
@@ -3173,20 +3671,30 @@
           <t>ANDRES BELLO</t>
         </is>
       </c>
-      <c r="G53" t="n">
-        <v>-12.04342</v>
-      </c>
-      <c r="H53" t="n">
-        <v>-75.255928</v>
-      </c>
-      <c r="I53" t="n">
-        <v>416</v>
-      </c>
-      <c r="J53" t="n">
-        <v>38</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0</v>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>-12.04342</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>-75.255928</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>416</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
@@ -3225,20 +3733,30 @@
           <t>30234 ROBERTO QUISPE POMALAZA</t>
         </is>
       </c>
-      <c r="G54" t="n">
-        <v>-11.942669</v>
-      </c>
-      <c r="H54" t="n">
-        <v>-75.258848</v>
-      </c>
-      <c r="I54" t="n">
-        <v>207</v>
-      </c>
-      <c r="J54" t="n">
-        <v>13</v>
-      </c>
-      <c r="K54" t="n">
-        <v>0</v>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>-11.942669</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>-75.258848</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
@@ -3277,20 +3795,30 @@
           <t>30235 VIRGEN DE FATIMA</t>
         </is>
       </c>
-      <c r="G55" t="n">
-        <v>-11.935335</v>
-      </c>
-      <c r="H55" t="n">
-        <v>-75.26039</v>
-      </c>
-      <c r="I55" t="n">
-        <v>207</v>
-      </c>
-      <c r="J55" t="n">
-        <v>13</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0</v>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>-11.935335</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>-75.26039</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -3329,20 +3857,30 @@
           <t>30238 ANDRES A. CACERES DORREGARAY</t>
         </is>
       </c>
-      <c r="G56" t="n">
-        <v>-11.99202</v>
-      </c>
-      <c r="H56" t="n">
-        <v>-75.24673</v>
-      </c>
-      <c r="I56" t="n">
-        <v>541</v>
-      </c>
-      <c r="J56" t="n">
-        <v>24</v>
-      </c>
-      <c r="K56" t="n">
-        <v>0</v>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>-11.99202</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>-75.24673</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>541</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
@@ -3381,20 +3919,30 @@
           <t>CHINCHAYSUYO</t>
         </is>
       </c>
-      <c r="G57" t="n">
-        <v>-12.1348</v>
-      </c>
-      <c r="H57" t="n">
-        <v>-75.16540000000001</v>
-      </c>
-      <c r="I57" t="n">
-        <v>545</v>
-      </c>
-      <c r="J57" t="n">
-        <v>43</v>
-      </c>
-      <c r="K57" t="n">
-        <v>0</v>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>-12.1348</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>-75.1654</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>545</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
@@ -3433,20 +3981,30 @@
           <t>30096</t>
         </is>
       </c>
-      <c r="G58" t="n">
-        <v>-12.01997</v>
-      </c>
-      <c r="H58" t="n">
-        <v>-75.28006999999999</v>
-      </c>
-      <c r="I58" t="n">
-        <v>361</v>
-      </c>
-      <c r="J58" t="n">
-        <v>14</v>
-      </c>
-      <c r="K58" t="n">
-        <v>0</v>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>-12.01997</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>-75.28007</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>361</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
@@ -3485,20 +4043,30 @@
           <t>SANTA BARBARA</t>
         </is>
       </c>
-      <c r="G59" t="n">
-        <v>-12.02066</v>
-      </c>
-      <c r="H59" t="n">
-        <v>-75.27988000000001</v>
-      </c>
-      <c r="I59" t="n">
-        <v>268</v>
-      </c>
-      <c r="J59" t="n">
-        <v>15</v>
-      </c>
-      <c r="K59" t="n">
-        <v>0</v>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>-12.02066</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>-75.27988</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
@@ -3537,20 +4105,30 @@
           <t>30108 JOSE MARIA ARGUEDAS ALTAMIRANO</t>
         </is>
       </c>
-      <c r="G60" t="n">
-        <v>-12.05206</v>
-      </c>
-      <c r="H60" t="n">
-        <v>-75.29105</v>
-      </c>
-      <c r="I60" t="n">
-        <v>231</v>
-      </c>
-      <c r="J60" t="n">
-        <v>12</v>
-      </c>
-      <c r="K60" t="n">
-        <v>0</v>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>-12.05206</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>-75.29105</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
@@ -3589,20 +4167,30 @@
           <t>SACO OLIVEROS</t>
         </is>
       </c>
-      <c r="G61" t="n">
-        <v>-12.05815</v>
-      </c>
-      <c r="H61" t="n">
-        <v>-75.20048</v>
-      </c>
-      <c r="I61" t="n">
-        <v>847</v>
-      </c>
-      <c r="J61" t="n">
-        <v>61</v>
-      </c>
-      <c r="K61" t="n">
-        <v>0</v>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>-12.05815</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>-75.20048</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>847</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
@@ -3641,20 +4229,30 @@
           <t>UNION</t>
         </is>
       </c>
-      <c r="G62" t="n">
-        <v>-12.03586</v>
-      </c>
-      <c r="H62" t="n">
-        <v>-75.19387999999999</v>
-      </c>
-      <c r="I62" t="n">
-        <v>614</v>
-      </c>
-      <c r="J62" t="n">
-        <v>28</v>
-      </c>
-      <c r="K62" t="n">
-        <v>0</v>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>-12.03586</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>-75.19388</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>614</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
@@ -3693,20 +4291,30 @@
           <t>MANUEL COVEÑAS</t>
         </is>
       </c>
-      <c r="G63" t="n">
-        <v>-12.07695</v>
-      </c>
-      <c r="H63" t="n">
-        <v>-75.2098</v>
-      </c>
-      <c r="I63" t="n">
-        <v>267</v>
-      </c>
-      <c r="J63" t="n">
-        <v>8</v>
-      </c>
-      <c r="K63" t="n">
-        <v>0</v>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>-12.07695</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>-75.2098</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
@@ -3745,20 +4353,30 @@
           <t>CIENTIFICA</t>
         </is>
       </c>
-      <c r="G64" t="n">
-        <v>-12.07373</v>
-      </c>
-      <c r="H64" t="n">
-        <v>-75.20649</v>
-      </c>
-      <c r="I64" t="n">
-        <v>1616</v>
-      </c>
-      <c r="J64" t="n">
-        <v>36</v>
-      </c>
-      <c r="K64" t="n">
-        <v>0</v>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>-12.07373</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>-75.20649</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1616</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
@@ -3797,20 +4415,30 @@
           <t>MI MUNDO INFANTIL SEÑOR DE LOS MILAGROS</t>
         </is>
       </c>
-      <c r="G65" t="n">
-        <v>-12.06784</v>
-      </c>
-      <c r="H65" t="n">
-        <v>-75.20309</v>
-      </c>
-      <c r="I65" t="n">
-        <v>213</v>
-      </c>
-      <c r="J65" t="n">
-        <v>11</v>
-      </c>
-      <c r="K65" t="n">
-        <v>0</v>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>-12.06784</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>-75.20309</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
@@ -3849,20 +4477,30 @@
           <t>30127 SAN FRANCISCO DE ASIS</t>
         </is>
       </c>
-      <c r="G66" t="n">
-        <v>-12.06872</v>
-      </c>
-      <c r="H66" t="n">
-        <v>-75.1994</v>
-      </c>
-      <c r="I66" t="n">
-        <v>330</v>
-      </c>
-      <c r="J66" t="n">
-        <v>22</v>
-      </c>
-      <c r="K66" t="n">
-        <v>1</v>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>-12.06872</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>-75.1994</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
@@ -3901,20 +4539,30 @@
           <t>JOSE CARLOS MARIATEGUI</t>
         </is>
       </c>
-      <c r="G67" t="n">
-        <v>-12.07785</v>
-      </c>
-      <c r="H67" t="n">
-        <v>-75.20778</v>
-      </c>
-      <c r="I67" t="n">
-        <v>1324</v>
-      </c>
-      <c r="J67" t="n">
-        <v>65</v>
-      </c>
-      <c r="K67" t="n">
-        <v>0</v>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>-12.07785</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>-75.20778</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1324</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
@@ -3953,20 +4601,30 @@
           <t>UNCP</t>
         </is>
       </c>
-      <c r="G68" t="n">
-        <v>-12.0721</v>
-      </c>
-      <c r="H68" t="n">
-        <v>-75.1961</v>
-      </c>
-      <c r="I68" t="n">
-        <v>231</v>
-      </c>
-      <c r="J68" t="n">
-        <v>19</v>
-      </c>
-      <c r="K68" t="n">
-        <v>0</v>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>-12.0721</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>-75.1961</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
@@ -4005,20 +4663,30 @@
           <t>TRILENIUM PRE UNI</t>
         </is>
       </c>
-      <c r="G69" t="n">
-        <v>-12.04599</v>
-      </c>
-      <c r="H69" t="n">
-        <v>-75.22423999999999</v>
-      </c>
-      <c r="I69" t="n">
-        <v>460</v>
-      </c>
-      <c r="J69" t="n">
-        <v>17</v>
-      </c>
-      <c r="K69" t="n">
-        <v>0</v>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>-12.04599</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>-75.22424</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>460</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
@@ -4057,20 +4725,30 @@
           <t>SAN PEDRO</t>
         </is>
       </c>
-      <c r="G70" t="n">
-        <v>-12.07799</v>
-      </c>
-      <c r="H70" t="n">
-        <v>-75.22523</v>
-      </c>
-      <c r="I70" t="n">
-        <v>210</v>
-      </c>
-      <c r="J70" t="n">
-        <v>15</v>
-      </c>
-      <c r="K70" t="n">
-        <v>0</v>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>-12.07799</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>-75.22523</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
@@ -4109,20 +4787,30 @@
           <t>LIRIOS DEL VALLE</t>
         </is>
       </c>
-      <c r="G71" t="n">
-        <v>-12.07149</v>
-      </c>
-      <c r="H71" t="n">
-        <v>-75.20372999999999</v>
-      </c>
-      <c r="I71" t="n">
-        <v>21</v>
-      </c>
-      <c r="J71" t="n">
-        <v>2</v>
-      </c>
-      <c r="K71" t="n">
-        <v>1</v>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>-12.07149</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>-75.20373</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
@@ -4161,20 +4849,30 @@
           <t>LOS PASITOS</t>
         </is>
       </c>
-      <c r="G72" t="n">
-        <v>-12.07359</v>
-      </c>
-      <c r="H72" t="n">
-        <v>-75.20995000000001</v>
-      </c>
-      <c r="I72" t="n">
-        <v>63</v>
-      </c>
-      <c r="J72" t="n">
-        <v>3</v>
-      </c>
-      <c r="K72" t="n">
-        <v>1</v>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>-12.07359</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>-75.20995</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
@@ -4213,20 +4911,30 @@
           <t>JOSE INGENIEROS</t>
         </is>
       </c>
-      <c r="G73" t="n">
-        <v>-12.07641</v>
-      </c>
-      <c r="H73" t="n">
-        <v>-75.20956</v>
-      </c>
-      <c r="I73" t="n">
-        <v>246</v>
-      </c>
-      <c r="J73" t="n">
-        <v>24</v>
-      </c>
-      <c r="K73" t="n">
-        <v>0</v>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>-12.07641</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>-75.20956</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
@@ -4265,20 +4973,30 @@
           <t>D'UNI</t>
         </is>
       </c>
-      <c r="G74" t="n">
-        <v>-12.07071</v>
-      </c>
-      <c r="H74" t="n">
-        <v>-75.19125</v>
-      </c>
-      <c r="I74" t="n">
-        <v>381</v>
-      </c>
-      <c r="J74" t="n">
-        <v>22</v>
-      </c>
-      <c r="K74" t="n">
-        <v>0</v>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>-12.07071</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>-75.19125</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>381</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
@@ -4317,20 +5035,30 @@
           <t>PREMIER SCHOOL</t>
         </is>
       </c>
-      <c r="G75" t="n">
-        <v>-12.0639</v>
-      </c>
-      <c r="H75" t="n">
-        <v>-75.2099</v>
-      </c>
-      <c r="I75" t="n">
-        <v>242</v>
-      </c>
-      <c r="J75" t="n">
-        <v>22</v>
-      </c>
-      <c r="K75" t="n">
-        <v>0</v>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>-12.0639</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-75.2099</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
@@ -4369,20 +5097,30 @@
           <t>TRILENIUM UNI - ING</t>
         </is>
       </c>
-      <c r="G76" t="n">
-        <v>-12.07564</v>
-      </c>
-      <c r="H76" t="n">
-        <v>-75.20962</v>
-      </c>
-      <c r="I76" t="n">
-        <v>436</v>
-      </c>
-      <c r="J76" t="n">
-        <v>19</v>
-      </c>
-      <c r="K76" t="n">
-        <v>0</v>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>-12.07564</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>-75.20962</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>436</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
@@ -4421,20 +5159,30 @@
           <t>FRANCOTIRADORES</t>
         </is>
       </c>
-      <c r="G77" t="n">
-        <v>-12.07456</v>
-      </c>
-      <c r="H77" t="n">
-        <v>-75.21843</v>
-      </c>
-      <c r="I77" t="n">
-        <v>258</v>
-      </c>
-      <c r="J77" t="n">
-        <v>13</v>
-      </c>
-      <c r="K77" t="n">
-        <v>0</v>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>-12.07456</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>-75.21843</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
@@ -4473,20 +5221,30 @@
           <t>INNOVA SCHOOLS HUANCAYO</t>
         </is>
       </c>
-      <c r="G78" t="n">
-        <v>-12.03791</v>
-      </c>
-      <c r="H78" t="n">
-        <v>-75.18858</v>
-      </c>
-      <c r="I78" t="n">
-        <v>1091</v>
-      </c>
-      <c r="J78" t="n">
-        <v>39</v>
-      </c>
-      <c r="K78" t="n">
-        <v>0</v>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>-12.03791</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>-75.18858</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>1091</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
@@ -4525,20 +5283,30 @@
           <t>FRIENDS GARDEN</t>
         </is>
       </c>
-      <c r="G79" t="n">
-        <v>-12.05488</v>
-      </c>
-      <c r="H79" t="n">
-        <v>-75.20419</v>
-      </c>
-      <c r="I79" t="n">
-        <v>350</v>
-      </c>
-      <c r="J79" t="n">
-        <v>23</v>
-      </c>
-      <c r="K79" t="n">
-        <v>0</v>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>-12.05488</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>-75.20419</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
@@ -4577,20 +5345,30 @@
           <t>30059 ROSA DE AMERICA</t>
         </is>
       </c>
-      <c r="G80" t="n">
-        <v>-12.04951</v>
-      </c>
-      <c r="H80" t="n">
-        <v>-75.20638</v>
-      </c>
-      <c r="I80" t="n">
-        <v>382</v>
-      </c>
-      <c r="J80" t="n">
-        <v>21</v>
-      </c>
-      <c r="K80" t="n">
-        <v>0</v>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>-12.04951</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>-75.20638</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
@@ -4629,20 +5407,30 @@
           <t>DIVINO MAESTRO JESUS</t>
         </is>
       </c>
-      <c r="G81" t="n">
-        <v>-12.05881</v>
-      </c>
-      <c r="H81" t="n">
-        <v>-75.21742</v>
-      </c>
-      <c r="I81" t="n">
-        <v>226</v>
-      </c>
-      <c r="J81" t="n">
-        <v>22</v>
-      </c>
-      <c r="K81" t="n">
-        <v>0</v>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>-12.05881</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>-75.21742</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
@@ -4681,20 +5469,30 @@
           <t>LIDERES PACIFISTAS</t>
         </is>
       </c>
-      <c r="G82" t="n">
-        <v>-12.07427</v>
-      </c>
-      <c r="H82" t="n">
-        <v>-75.21111999999999</v>
-      </c>
-      <c r="I82" t="n">
-        <v>49</v>
-      </c>
-      <c r="J82" t="n">
-        <v>9</v>
-      </c>
-      <c r="K82" t="n">
-        <v>1</v>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>-12.07427</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>-75.21112</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
@@ -4733,20 +5531,30 @@
           <t>DANIEL ALCIDES CARRION</t>
         </is>
       </c>
-      <c r="G83" t="n">
-        <v>-12.07115</v>
-      </c>
-      <c r="H83" t="n">
-        <v>-75.22917</v>
-      </c>
-      <c r="I83" t="n">
-        <v>288</v>
-      </c>
-      <c r="J83" t="n">
-        <v>18</v>
-      </c>
-      <c r="K83" t="n">
-        <v>0</v>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>-12.07115</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>-75.22917</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/JUNIN-HUANCAYO-HUANCAYO.xlsx
+++ b/ZonasEscolares/excels/JUNIN-HUANCAYO-HUANCAYO.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>219659</t>
+          <t>640786</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>MI MUNDO INFANTIL SEÑOR DE LOS MILAGROS</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-12.07044</t>
+          <t>-12.06784</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-75.21324</t>
+          <t>-75.20309</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>292</t>
+          <t>213</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>219664</t>
+          <t>220097</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>254 OLIMPIA SANCHEZ MORENO</t>
+          <t>NUESTRA SEÑORA DE COCHARCAS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-12.06</t>
+          <t>-12.07517</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-75.203</t>
+          <t>-75.20169</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>2143</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>114</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -598,7 +598,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>219678</t>
+          <t>219796</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>30003 PEDRO R. DIAZ HUAMAN</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-12.073669</t>
+          <t>-12.02444</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-75.199981</t>
+          <t>-75.18406</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>481</t>
+          <t>238</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>219683</t>
+          <t>248505</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>30320 JESUS EL NAZARENO</t>
+          <t>30108 JOSE MARIA ARGUEDAS ALTAMIRANO</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-12.0736</t>
+          <t>-12.05206</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-75.2241</t>
+          <t>-75.29105</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>476</t>
+          <t>231</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>219720</t>
+          <t>219857</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>DANIEL ALCIDES CARRION</t>
+          <t>MARIA INMACULADA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-12.07986</t>
+          <t>-12.06567</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-75.22491</t>
+          <t>-75.20904</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>1672</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>121</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>219763</t>
+          <t>219659</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>253</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-12.0506</t>
+          <t>-12.07044</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-75.199</t>
+          <t>-75.21324</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>292</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>219777</t>
+          <t>225976</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>30234 ROBERTO QUISPE POMALAZA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-12.0713</t>
+          <t>-11.942669</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-75.2048</t>
+          <t>-75.258848</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>207</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>219782</t>
+          <t>225981</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>30001 SANTA ROSA DE LIMA</t>
+          <t>30235 VIRGEN DE FATIMA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-12.0544</t>
+          <t>-11.935335</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-75.1886</t>
+          <t>-75.26039</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>207</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>219796</t>
+          <t>808295</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>30003 PEDRO R. DIAZ HUAMAN</t>
+          <t>FRANCOTIRADORES</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-12.02444</t>
+          <t>-12.07456</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-75.18406</t>
+          <t>-75.21843</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>258</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>219800</t>
+          <t>219720</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>30005 SAN FRANCISCO DE ASIS / 30005 SAN FRANSISCO DE ASIS</t>
+          <t>DANIEL ALCIDES CARRION</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-12.0338</t>
+          <t>-12.07986</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-75.1909</t>
+          <t>-75.22491</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>426</t>
+          <t>260</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>219824</t>
+          <t>219777</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>30009 VIRGEN DE GUADALUPE</t>
+          <t>465</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-12.043</t>
+          <t>-12.0713</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-75.1946</t>
+          <t>-75.2048</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>566</t>
+          <t>280</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>219838</t>
+          <t>219782</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>30011 VIRGEN DEL CARMEN</t>
+          <t>30001 SANTA ROSA DE LIMA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-12.06016</t>
+          <t>-12.0544</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-75.194</t>
+          <t>-75.1886</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>322</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>219843</t>
+          <t>220790</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>30054 SANTA MARIA REYNA</t>
+          <t>SAN JUAN BOSCO</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-12.070532</t>
+          <t>-12.06867</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-75.211277</t>
+          <t>-75.2136</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>858</t>
+          <t>348</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>219857</t>
+          <t>224585</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MARIA INMACULADA</t>
+          <t>30227</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-12.06567</t>
+          <t>-11.97212</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-75.20904</t>
+          <t>-75.25221</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1672</t>
+          <t>293</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>219862</t>
+          <t>226650</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>30057 / 30057 MARIA DE FATIMA</t>
+          <t>30096</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-12.0761</t>
+          <t>-12.01997</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-75.2133</t>
+          <t>-75.28007</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>361</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>219876</t>
+          <t>219923</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>30059 ROSA DE AMERICA</t>
+          <t>31458 SAN JUDAS TADEO</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-12.06955</t>
+          <t>-12.0676</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-75.21345</t>
+          <t>-75.1937</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>204</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,22 +1493,22 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>219881</t>
+          <t>226674</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>30124 SAN FRANCISCO DE ASIS</t>
+          <t>SANTA BARBARA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-12.06633</t>
+          <t>-12.02066</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-75.19819</t>
+          <t>-75.27988</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1518,7 +1518,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>219904</t>
+          <t>650582</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>30128</t>
+          <t>SAN PEDRO</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-12.0577</t>
+          <t>-12.07799</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-75.18715</t>
+          <t>-75.22523</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>337</t>
+          <t>210</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>219923</t>
+          <t>219664</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>31458 SAN JUDAS TADEO</t>
+          <t>254 OLIMPIA SANCHEZ MORENO</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-12.0676</t>
+          <t>-12.06</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-75.1937</t>
+          <t>-75.203</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>391</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>219942</t>
+          <t>219881</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>31506 SAGRADO CORAZON DE JESUS</t>
+          <t>30124 SAN FRANCISCO DE ASIS</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-12.07186</t>
+          <t>-12.06633</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-75.21074</t>
+          <t>-75.19819</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>268</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>219956</t>
+          <t>224873</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>31507 DOMINGO F. SARMIENTO</t>
+          <t>30175</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-12.06955</t>
+          <t>-12.12248</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-75.20631</t>
+          <t>-75.21542</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>744</t>
+          <t>288</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>219961</t>
+          <t>219763</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>31540 SANTA ISABEL</t>
+          <t>372</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-12.05764</t>
+          <t>-12.0506</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-75.20275</t>
+          <t>-75.199</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1518</t>
+          <t>263</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>219975</t>
+          <t>221426</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>31541 EMMA LUZMILA CALLE VERGARA</t>
+          <t>SAN CARLOS</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-12.06587</t>
+          <t>-12.05908</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-75.20936</t>
+          <t>-75.20615</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1028</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>219980</t>
+          <t>641842</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>31542 VIRGEN MARIA ADMIRABLE</t>
+          <t>TRILENIUM PRE UNI</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-12.073551</t>
+          <t>-12.04599</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-75.199432</t>
+          <t>-75.22424</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1091</t>
+          <t>460</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,42 +1989,42 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>219999</t>
+          <t>219800</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>31554 JOSE C. MARIATEGUI</t>
+          <t>30005 SAN FRANCISCO DE ASIS / 30005 SAN FRANSISCO DE ASIS</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-12.07723</t>
+          <t>-12.0338</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-75.20809</t>
+          <t>-75.1909</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>426</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>220035</t>
+          <t>219904</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>VIRGEN DE FATIMA</t>
+          <t>30128</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-12.05792</t>
+          <t>-12.0577</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-75.19586</t>
+          <t>-75.18715</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>718</t>
+          <t>337</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>220064</t>
+          <t>220101</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>PILOTO SANTA ISABEL</t>
+          <t>SAN FRANCISCO DE ASIS</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-12.05843</t>
+          <t>-12.06401</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-75.20263</t>
+          <t>-75.18805</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>3648</t>
+          <t>262</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>220097</t>
+          <t>220304</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE COCHARCAS</t>
+          <t>GOTITAS DE ROCIO</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-12.07517</t>
+          <t>-12.05834</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-75.20169</t>
+          <t>-75.2067</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2143</t>
+          <t>295</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2237,27 +2237,27 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>220101</t>
+          <t>858822</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>SAN FRANCISCO DE ASIS</t>
+          <t>DANIEL ALCIDES CARRION</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-12.06401</t>
+          <t>-12.07115</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-75.18805</t>
+          <t>-75.22917</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>288</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>220115</t>
+          <t>641762</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>LOS ANDES</t>
+          <t>UNCP</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-12.02506</t>
+          <t>-12.0721</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-75.18379</t>
+          <t>-75.1961</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>231</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>220120</t>
+          <t>808257</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DEL ROSARIO</t>
+          <t>TRILENIUM UNI - ING</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-12.06998</t>
+          <t>-12.07564</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-75.21226</t>
+          <t>-75.20962</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>436</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2423,37 +2423,37 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>220163</t>
+          <t>750529</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>SANTA MARIA REYNA</t>
+          <t>LIRIOS DEL VALLE</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-12.07529</t>
+          <t>-12.07149</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-75.22055</t>
+          <t>-75.20373</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>731</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>220177</t>
+          <t>219678</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>31363 LA ASUNCION / 406 LA ASUNCION / LA ASUNCION</t>
+          <t>300</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-12.029846</t>
+          <t>-12.073669</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-75.190427</t>
+          <t>-75.199981</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1075</t>
+          <t>481</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>220200</t>
+          <t>220064</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CLARETIANO</t>
+          <t>PILOTO SANTA ISABEL</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-12.06242</t>
+          <t>-12.05843</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-75.20534</t>
+          <t>-75.20263</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>981</t>
+          <t>3648</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>209</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>220224</t>
+          <t>220115</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>ANDINO</t>
+          <t>LOS ANDES</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-12.06371</t>
+          <t>-12.02506</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-75.2065</t>
+          <t>-75.18379</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>795</t>
+          <t>253</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>220304</t>
+          <t>220634</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>GOTITAS DE ROCIO</t>
+          <t>COLEGIO ADVENTISTA HUANCAYO</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-12.05834</t>
+          <t>-12.07209</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-75.2067</t>
+          <t>-75.21168</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>328</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,37 +2733,37 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>220479</t>
+          <t>835166</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>ROSA DE SANTA MARIA</t>
+          <t>30059 ROSA DE AMERICA</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-12.073214</t>
+          <t>-12.04951</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-75.198074</t>
+          <t>-75.20638</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>382</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2795,37 +2795,37 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>220634</t>
+          <t>641489</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>COLEGIO ADVENTISTA HUANCAYO</t>
+          <t>30127 SAN FRANCISCO DE ASIS</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-12.07209</t>
+          <t>-12.06872</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-75.21168</t>
+          <t>-75.1994</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>330</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>220728</t>
+          <t>778849</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>RAMIRO VILLAVERDE LAZO</t>
+          <t>D'UNI</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-12.05737</t>
+          <t>-12.07071</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-75.19264</t>
+          <t>-75.19125</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>381</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>220790</t>
+          <t>804023</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>SAN JUAN BOSCO</t>
+          <t>PREMIER SCHOOL</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-12.06867</t>
+          <t>-12.0639</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-75.2136</t>
+          <t>-75.2099</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>242</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>220832</t>
+          <t>838886</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>ZARATE</t>
+          <t>DIVINO MAESTRO JESUS</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-12.06021</t>
+          <t>-12.05881</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-75.20687</t>
+          <t>-75.21742</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1356</t>
+          <t>226</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3043,32 +3043,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>221426</t>
+          <t>825394</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>SAN CARLOS</t>
+          <t>FRIENDS GARDEN</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-12.05908</t>
+          <t>-12.05488</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-75.20615</t>
+          <t>-75.20419</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>350</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3105,32 +3105,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>222906</t>
+          <t>219838</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>30209</t>
+          <t>30011 VIRGEN DEL CARMEN</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-12.02922</t>
+          <t>-12.06016</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-75.22824</t>
+          <t>-75.194</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>802</t>
+          <t>372</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3167,32 +3167,32 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>223086</t>
+          <t>224608</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>31509 / 31509 RICARDO MENENDEZ MENENDEZ</t>
+          <t>JOSE OLAYA</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-12.0597</t>
+          <t>-11.9746</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-75.2178</t>
+          <t>-75.2568</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1144</t>
+          <t>320</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3229,32 +3229,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>223133</t>
+          <t>226075</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>31595 / 31595 FLORENCIO V. HINOSTROZA C.</t>
+          <t>30238 ANDRES A. CACERES DORREGARAY</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-12.0253</t>
+          <t>-11.99202</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-75.23659</t>
+          <t>-75.24673</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>541</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3291,32 +3291,32 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>223246</t>
+          <t>756512</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>MARISCAL CASTILLA</t>
+          <t>JOSE INGENIEROS</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-12.05916</t>
+          <t>-12.07641</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-75.21802</t>
+          <t>-75.20956</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2302</t>
+          <t>246</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3353,32 +3353,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>224585</t>
+          <t>224670</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>30227</t>
+          <t>30172</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-11.97212</t>
+          <t>-12.11</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-75.25221</t>
+          <t>-75.2021</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>535</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3415,32 +3415,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>224608</t>
+          <t>219683</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>JOSE OLAYA</t>
+          <t>30320 JESUS EL NAZARENO</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-11.9746</t>
+          <t>-12.0736</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-75.2568</t>
+          <t>-75.2241</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>476</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3477,32 +3477,32 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>224670</t>
+          <t>219862</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>30172</t>
+          <t>30057 / 30057 MARIA DE FATIMA</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-12.11</t>
+          <t>-12.0761</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-75.2021</t>
+          <t>-75.2133</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>535</t>
+          <t>576</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>224868</t>
+          <t>223133</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>30173</t>
+          <t>31595 / 31595 FLORENCIO V. HINOSTROZA C.</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-12.136861</t>
+          <t>-12.0253</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>-75.222522</t>
+          <t>-75.23659</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>551</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>224873</t>
+          <t>625291</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>30175</t>
+          <t>UNION</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-12.12248</t>
+          <t>-12.03586</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>-75.21542</t>
+          <t>-75.19388</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>614</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3663,37 +3663,37 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>225636</t>
+          <t>754674</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>ANDRES BELLO</t>
+          <t>LOS PASITOS</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-12.04342</t>
+          <t>-12.07359</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>-75.255928</t>
+          <t>-75.20995</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>416</t>
+          <t>63</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3725,32 +3725,32 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>225976</t>
+          <t>219824</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>30234 ROBERTO QUISPE POMALAZA</t>
+          <t>30009 VIRGEN DE GUADALUPE</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-11.942669</t>
+          <t>-12.043</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>-75.258848</t>
+          <t>-75.1946</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>566</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3787,32 +3787,32 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>225981</t>
+          <t>219942</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>30235 VIRGEN DE FATIMA</t>
+          <t>31506 SAGRADO CORAZON DE JESUS</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-11.935335</t>
+          <t>-12.07186</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>-75.26039</t>
+          <t>-75.21074</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>644</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3849,32 +3849,32 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>226075</t>
+          <t>219956</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>30238 ANDRES A. CACERES DORREGARAY</t>
+          <t>31507 DOMINGO F. SARMIENTO</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-11.99202</t>
+          <t>-12.06955</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>-75.24673</t>
+          <t>-75.20631</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>541</t>
+          <t>744</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3911,32 +3911,32 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>226551</t>
+          <t>224868</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>CHINCHAYSUYO</t>
+          <t>30173</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-12.1348</t>
+          <t>-12.136861</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>-75.1654</t>
+          <t>-75.222522</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>545</t>
+          <t>895</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3973,32 +3973,32 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>226650</t>
+          <t>640625</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>30096</t>
+          <t>CIENTIFICA</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-12.01997</t>
+          <t>-12.07373</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>-75.28007</t>
+          <t>-75.20649</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4035,32 +4035,32 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>226674</t>
+          <t>219843</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>SANTA BARBARA</t>
+          <t>30054 SANTA MARIA REYNA</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-12.02066</t>
+          <t>-12.070532</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>-75.27988</t>
+          <t>-75.211277</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>268</t>
+          <t>858</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4097,32 +4097,32 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>248505</t>
+          <t>225636</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>30108 JOSE MARIA ARGUEDAS ALTAMIRANO</t>
+          <t>ANDRES BELLO</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-12.05206</t>
+          <t>-12.04342</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>-75.29105</t>
+          <t>-75.255928</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>416</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4159,32 +4159,32 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>517649</t>
+          <t>222906</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>SACO OLIVEROS</t>
+          <t>30209</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-12.05815</t>
+          <t>-12.02922</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>-75.20048</t>
+          <t>-75.22824</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>847</t>
+          <t>802</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4221,32 +4221,32 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>625291</t>
+          <t>808318</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>UNION</t>
+          <t>INNOVA SCHOOLS HUANCAYO</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>-12.03586</t>
+          <t>-12.03791</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>-75.19388</t>
+          <t>-75.18858</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>1091</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -4283,37 +4283,37 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>640461</t>
+          <t>220479</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>MANUEL COVEÑAS</t>
+          <t>ROSA DE SANTA MARIA</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>-12.07695</t>
+          <t>-12.073214</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>-75.2098</t>
+          <t>-75.198074</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>99</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4345,32 +4345,32 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>640625</t>
+          <t>226551</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>CIENTIFICA</t>
+          <t>CHINCHAYSUYO</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>-12.07373</t>
+          <t>-12.1348</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>-75.20649</t>
+          <t>-75.1654</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>545</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>43</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4407,32 +4407,32 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>640786</t>
+          <t>220163</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>MI MUNDO INFANTIL SEÑOR DE LOS MILAGROS</t>
+          <t>SANTA MARIA REYNA</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>-12.06784</t>
+          <t>-12.07529</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>-75.20309</t>
+          <t>-75.22055</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>731</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>46</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4469,37 +4469,37 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>641489</t>
+          <t>219876</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>30127 SAN FRANCISCO DE ASIS</t>
+          <t>30059 ROSA DE AMERICA</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>-12.06872</t>
+          <t>-12.06955</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>-75.1994</t>
+          <t>-75.21345</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>1246</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>49</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4531,32 +4531,32 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>641559</t>
+          <t>219975</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>JOSE CARLOS MARIATEGUI</t>
+          <t>31541 EMMA LUZMILA CALLE VERGARA</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>-12.07785</t>
+          <t>-12.06587</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>-75.20778</t>
+          <t>-75.20936</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>1324</t>
+          <t>1028</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>49</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4593,32 +4593,32 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>641762</t>
+          <t>220035</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>UNCP</t>
+          <t>VIRGEN DE FATIMA</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>-12.0721</t>
+          <t>-12.05792</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>-75.1961</t>
+          <t>-75.19586</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>718</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4655,32 +4655,32 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>641842</t>
+          <t>220832</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>TRILENIUM PRE UNI</t>
+          <t>ZARATE</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>-12.04599</t>
+          <t>-12.06021</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>-75.22424</t>
+          <t>-75.20687</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>460</t>
+          <t>1356</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4717,37 +4717,37 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>650582</t>
+          <t>219999</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>SAN PEDRO</t>
+          <t>31554 JOSE C. MARIATEGUI</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>-12.07799</t>
+          <t>-12.07723</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>-75.22523</t>
+          <t>-75.20809</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>894</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>53</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -4779,37 +4779,37 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>750529</t>
+          <t>219980</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>LIRIOS DEL VALLE</t>
+          <t>31542 VIRGEN MARIA ADMIRABLE</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>-12.07149</t>
+          <t>-12.073551</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>-75.20373</t>
+          <t>-75.199432</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>1091</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>54</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -4841,42 +4841,42 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>754674</t>
+          <t>220177</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>LOS PASITOS</t>
+          <t>31363 LA ASUNCION / 406 LA ASUNCION / LA ASUNCION</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>-12.07359</t>
+          <t>-12.029846</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>-75.20995</t>
+          <t>-75.190427</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>1075</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>54</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4903,32 +4903,32 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>756512</t>
+          <t>223086</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>JOSE INGENIEROS</t>
+          <t>31509 / 31509 RICARDO MENENDEZ MENENDEZ</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>-12.07641</t>
+          <t>-12.0597</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>-75.20956</t>
+          <t>-75.2178</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>1144</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>56</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -4965,32 +4965,32 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>778849</t>
+          <t>220200</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>D'UNI</t>
+          <t>CLARETIANO</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>-12.07071</t>
+          <t>-12.06242</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>-75.19125</t>
+          <t>-75.20534</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>981</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>57</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -5027,32 +5027,32 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>804023</t>
+          <t>219961</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>PREMIER SCHOOL</t>
+          <t>31540 SANTA ISABEL</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>-12.0639</t>
+          <t>-12.05764</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>-75.2099</t>
+          <t>-75.20275</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>1518</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>59</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -5089,32 +5089,32 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>808257</t>
+          <t>220728</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>TRILENIUM UNI - ING</t>
+          <t>RAMIRO VILLAVERDE LAZO</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>-12.07564</t>
+          <t>-12.05737</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>-75.20962</t>
+          <t>-75.19264</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>436</t>
+          <t>933</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>60</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -5151,32 +5151,32 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>808295</t>
+          <t>220224</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>FRANCOTIRADORES</t>
+          <t>ANDINO</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>-12.07456</t>
+          <t>-12.06371</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>-75.21843</t>
+          <t>-75.2065</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>795</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>61</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5213,32 +5213,32 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>808318</t>
+          <t>517649</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>INNOVA SCHOOLS HUANCAYO</t>
+          <t>SACO OLIVEROS</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>-12.03791</t>
+          <t>-12.05815</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>-75.18858</t>
+          <t>-75.20048</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>1091</t>
+          <t>847</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>61</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -5275,32 +5275,32 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>825394</t>
+          <t>641559</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>FRIENDS GARDEN</t>
+          <t>JOSE CARLOS MARIATEGUI</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>-12.05488</t>
+          <t>-12.07785</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>-75.20419</t>
+          <t>-75.20778</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>1324</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>65</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -5337,32 +5337,32 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>835166</t>
+          <t>640461</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>30059 ROSA DE AMERICA</t>
+          <t>MANUEL COVEÑAS</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>-12.04951</t>
+          <t>-12.07695</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>-75.20638</t>
+          <t>-75.2098</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>267</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -5399,32 +5399,32 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>838886</t>
+          <t>223246</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>DIVINO MAESTRO JESUS</t>
+          <t>MARISCAL CASTILLA</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>-12.05881</t>
+          <t>-12.05916</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>-75.21742</t>
+          <t>-75.21802</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>2302</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>85</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -5523,32 +5523,32 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>858822</t>
+          <t>220120</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>DANIEL ALCIDES CARRION</t>
+          <t>NUESTRA SEÑORA DEL ROSARIO</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>-12.07115</t>
+          <t>-12.06998</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>-75.22917</t>
+          <t>-75.21226</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>98</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">

--- a/ZonasEscolares/excels/JUNIN-HUANCAYO-HUANCAYO.xlsx
+++ b/ZonasEscolares/excels/JUNIN-HUANCAYO-HUANCAYO.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>640786</t>
+          <t>858822</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>MI MUNDO INFANTIL SEÑOR DE LOS MILAGROS</t>
+          <t>DANIEL ALCIDES CARRION</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-12.06784</t>
+          <t>288</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-75.20309</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>-12.07115</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-75.22917</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,37 +563,37 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>220097</t>
+          <t>843915</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE COCHARCAS</t>
+          <t>LIDERES PACIFISTAS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-12.07517</t>
+          <t>49</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-75.20169</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2143</t>
+          <t>-12.07427</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>-75.21112</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>219796</t>
+          <t>838886</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>30003 PEDRO R. DIAZ HUAMAN</t>
+          <t>DIVINO MAESTRO JESUS</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-12.02444</t>
+          <t>226</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-75.18406</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>-12.05881</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-75.21742</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>248505</t>
+          <t>835166</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>30108 JOSE MARIA ARGUEDAS ALTAMIRANO</t>
+          <t>30059 ROSA DE AMERICA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-12.05206</t>
+          <t>382</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-75.29105</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>-12.04951</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-75.20638</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>219857</t>
+          <t>825394</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MARIA INMACULADA</t>
+          <t>FRIENDS GARDEN</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-12.06567</t>
+          <t>350</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-75.20904</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1672</t>
+          <t>-12.05488</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>-75.20419</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>219659</t>
+          <t>808318</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>INNOVA SCHOOLS HUANCAYO</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-12.07044</t>
+          <t>1091</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-75.21324</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>292</t>
+          <t>-12.03791</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-75.18858</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>225976</t>
+          <t>808295</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>30234 ROBERTO QUISPE POMALAZA</t>
+          <t>FRANCOTIRADORES</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-11.942669</t>
+          <t>258</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-75.258848</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>-12.07456</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-75.21843</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>225981</t>
+          <t>808257</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>30235 VIRGEN DE FATIMA</t>
+          <t>TRILENIUM UNI - ING</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-11.935335</t>
+          <t>436</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-75.26039</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>-12.07564</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-75.20962</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>808295</t>
+          <t>804023</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>FRANCOTIRADORES</t>
+          <t>PREMIER SCHOOL</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-12.07456</t>
+          <t>242</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-75.21843</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>-12.0639</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-75.2099</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>219720</t>
+          <t>778849</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>DANIEL ALCIDES CARRION</t>
+          <t>D'UNI</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-12.07986</t>
+          <t>381</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-75.22491</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>-12.07071</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-75.19125</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>219777</t>
+          <t>756512</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>JOSE INGENIEROS</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-12.0713</t>
+          <t>246</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-75.2048</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>-12.07641</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-75.20956</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,37 +1183,37 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>219782</t>
+          <t>754674</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>30001 SANTA ROSA DE LIMA</t>
+          <t>LOS PASITOS</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-12.0544</t>
+          <t>63</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-75.1886</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>-12.07359</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-75.20995</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1245,37 +1245,37 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>220790</t>
+          <t>750529</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SAN JUAN BOSCO</t>
+          <t>LIRIOS DEL VALLE</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-12.06867</t>
+          <t>21</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-75.2136</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>-12.07149</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-75.20373</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>224585</t>
+          <t>650582</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>30227</t>
+          <t>SAN PEDRO</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-11.97212</t>
+          <t>210</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-75.25221</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>-12.07799</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-75.22523</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>226650</t>
+          <t>641842</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>30096</t>
+          <t>TRILENIUM PRE UNI</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-12.01997</t>
+          <t>460</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-75.28007</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>-12.04599</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-75.22424</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>219923</t>
+          <t>641762</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>31458 SAN JUDAS TADEO</t>
+          <t>UNCP</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-12.0676</t>
+          <t>231</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-75.1937</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>-12.0721</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-75.1961</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>226674</t>
+          <t>641559</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>SANTA BARBARA</t>
+          <t>JOSE CARLOS MARIATEGUI</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-12.02066</t>
+          <t>1324</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-75.27988</t>
+          <t>65</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>268</t>
+          <t>-12.07785</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-75.20778</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,37 +1555,37 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>650582</t>
+          <t>641489</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>SAN PEDRO</t>
+          <t>30127 SAN FRANCISCO DE ASIS</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-12.07799</t>
+          <t>330</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-75.22523</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>-12.06872</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-75.1994</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>219664</t>
+          <t>640786</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>254 OLIMPIA SANCHEZ MORENO</t>
+          <t>MI MUNDO INFANTIL SEÑOR DE LOS MILAGROS</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-12.06</t>
+          <t>213</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-75.203</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>-12.06784</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-75.20309</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>219881</t>
+          <t>640625</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>30124 SAN FRANCISCO DE ASIS</t>
+          <t>CIENTIFICA</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-12.06633</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-75.19819</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>268</t>
+          <t>-12.07373</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-75.20649</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>224873</t>
+          <t>640461</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>30175</t>
+          <t>MANUEL COVEÑAS</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-12.12248</t>
+          <t>267</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-75.21542</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>-12.07695</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-75.2098</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>219763</t>
+          <t>625291</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>UNION</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-12.0506</t>
+          <t>614</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-75.199</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>-12.03586</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-75.19388</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>221426</t>
+          <t>517649</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SAN CARLOS</t>
+          <t>SACO OLIVEROS</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-12.05908</t>
+          <t>847</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-75.20615</t>
+          <t>61</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>-12.05815</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-75.20048</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>641842</t>
+          <t>248505</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>TRILENIUM PRE UNI</t>
+          <t>30108 JOSE MARIA ARGUEDAS ALTAMIRANO</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-12.04599</t>
+          <t>231</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-75.22424</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>460</t>
+          <t>-12.05206</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-75.29105</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>219800</t>
+          <t>226674</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>30005 SAN FRANCISCO DE ASIS / 30005 SAN FRANSISCO DE ASIS</t>
+          <t>SANTA BARBARA</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-12.0338</t>
+          <t>268</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-75.1909</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>426</t>
+          <t>-12.02066</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-75.27988</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>219904</t>
+          <t>226650</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>30128</t>
+          <t>30096</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-12.0577</t>
+          <t>361</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-75.18715</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>337</t>
+          <t>-12.01997</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-75.28007</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>220101</t>
+          <t>226551</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>SAN FRANCISCO DE ASIS</t>
+          <t>CHINCHAYSUYO</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-12.06401</t>
+          <t>545</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-75.18805</t>
+          <t>43</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>-12.1348</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-75.1654</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>220304</t>
+          <t>226075</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>GOTITAS DE ROCIO</t>
+          <t>30238 ANDRES A. CACERES DORREGARAY</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-12.05834</t>
+          <t>541</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-75.2067</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>-11.99202</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-75.24673</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>858822</t>
+          <t>225981</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>DANIEL ALCIDES CARRION</t>
+          <t>30235 VIRGEN DE FATIMA</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-12.07115</t>
+          <t>207</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-75.22917</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>-11.935335</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-75.26039</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>641762</t>
+          <t>225976</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>UNCP</t>
+          <t>30234 ROBERTO QUISPE POMALAZA</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-12.0721</t>
+          <t>207</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-75.1961</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>-11.942669</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-75.258848</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>808257</t>
+          <t>225636</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>TRILENIUM UNI - ING</t>
+          <t>ANDRES BELLO</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-12.07564</t>
+          <t>416</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-75.20962</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>436</t>
+          <t>-12.04342</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-75.255928</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2423,37 +2423,37 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>750529</t>
+          <t>224873</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>LIRIOS DEL VALLE</t>
+          <t>30175</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-12.07149</t>
+          <t>288</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-75.20373</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-12.12248</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>-75.21542</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>219678</t>
+          <t>224868</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>30173</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-12.073669</t>
+          <t>895</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-75.199981</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>481</t>
+          <t>-12.136861</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-75.222522</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>220064</t>
+          <t>224670</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>PILOTO SANTA ISABEL</t>
+          <t>30172</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-12.05843</t>
+          <t>535</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-75.20263</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>3648</t>
+          <t>-12.11</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>-75.2021</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>220115</t>
+          <t>224608</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>LOS ANDES</t>
+          <t>JOSE OLAYA</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-12.02506</t>
+          <t>320</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-75.18379</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>-11.9746</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-75.2568</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>220634</t>
+          <t>224585</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>COLEGIO ADVENTISTA HUANCAYO</t>
+          <t>30227</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-12.07209</t>
+          <t>293</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-75.21168</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>-11.97212</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-75.25221</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>835166</t>
+          <t>223246</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>30059 ROSA DE AMERICA</t>
+          <t>MARISCAL CASTILLA</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-12.04951</t>
+          <t>2302</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-75.20638</t>
+          <t>85</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>-12.05916</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-75.21802</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2795,37 +2795,37 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>641489</t>
+          <t>223133</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>30127 SAN FRANCISCO DE ASIS</t>
+          <t>31595 / 31595 FLORENCIO V. HINOSTROZA C.</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-12.06872</t>
+          <t>551</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-75.1994</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>-12.0253</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-75.23659</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>778849</t>
+          <t>223086</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>D'UNI</t>
+          <t>31509 / 31509 RICARDO MENENDEZ MENENDEZ</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-12.07071</t>
+          <t>1144</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-75.19125</t>
+          <t>56</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>-12.0597</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-75.2178</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>804023</t>
+          <t>222906</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>PREMIER SCHOOL</t>
+          <t>30209</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-12.0639</t>
+          <t>802</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-75.2099</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>-12.02922</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-75.22824</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>838886</t>
+          <t>221426</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>DIVINO MAESTRO JESUS</t>
+          <t>SAN CARLOS</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-12.05881</t>
+          <t>250</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-75.21742</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>-12.05908</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-75.20615</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3043,32 +3043,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>825394</t>
+          <t>220832</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>FRIENDS GARDEN</t>
+          <t>ZARATE</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-12.05488</t>
+          <t>1356</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-75.20419</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>-12.06021</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-75.20687</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3105,32 +3105,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>219838</t>
+          <t>220790</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>30011 VIRGEN DEL CARMEN</t>
+          <t>SAN JUAN BOSCO</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-12.06016</t>
+          <t>348</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-75.194</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>-12.06867</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-75.2136</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3167,32 +3167,32 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>224608</t>
+          <t>220728</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>JOSE OLAYA</t>
+          <t>RAMIRO VILLAVERDE LAZO</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-11.9746</t>
+          <t>933</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-75.2568</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>-12.05737</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-75.19264</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3229,32 +3229,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>226075</t>
+          <t>220634</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>30238 ANDRES A. CACERES DORREGARAY</t>
+          <t>COLEGIO ADVENTISTA HUANCAYO</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-11.99202</t>
+          <t>328</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-75.24673</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>541</t>
+          <t>-12.07209</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-75.21168</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3291,37 +3291,37 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>756512</t>
+          <t>220479</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>JOSE INGENIEROS</t>
+          <t>ROSA DE SANTA MARIA</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-12.07641</t>
+          <t>99</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-75.20956</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>-12.073214</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-75.198074</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3353,32 +3353,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>224670</t>
+          <t>220304</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>30172</t>
+          <t>GOTITAS DE ROCIO</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-12.11</t>
+          <t>295</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-75.2021</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>535</t>
+          <t>-12.05834</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-75.2067</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3415,32 +3415,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>219683</t>
+          <t>220224</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>30320 JESUS EL NAZARENO</t>
+          <t>ANDINO</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-12.0736</t>
+          <t>795</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-75.2241</t>
+          <t>61</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>476</t>
+          <t>-12.06371</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-75.2065</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3477,32 +3477,32 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>219862</t>
+          <t>220200</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>30057 / 30057 MARIA DE FATIMA</t>
+          <t>CLARETIANO</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-12.0761</t>
+          <t>981</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-75.2133</t>
+          <t>57</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>-12.06242</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-75.20534</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>223133</t>
+          <t>220177</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>31595 / 31595 FLORENCIO V. HINOSTROZA C.</t>
+          <t>31363 LA ASUNCION / 406 LA ASUNCION / LA ASUNCION</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-12.0253</t>
+          <t>1075</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>-75.23659</t>
+          <t>54</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>-12.029846</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-75.190427</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3601,32 +3601,32 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>625291</t>
+          <t>220163</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>UNION</t>
+          <t>SANTA MARIA REYNA</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-12.03586</t>
+          <t>731</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>-75.19388</t>
+          <t>46</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>-12.07529</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-75.22055</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3663,37 +3663,37 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>754674</t>
+          <t>220120</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>LOS PASITOS</t>
+          <t>NUESTRA SEÑORA DEL ROSARIO</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-12.07359</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>-75.20995</t>
+          <t>98</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>-12.06998</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-75.21226</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3725,32 +3725,32 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>219824</t>
+          <t>220115</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>30009 VIRGEN DE GUADALUPE</t>
+          <t>LOS ANDES</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-12.043</t>
+          <t>253</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>-75.1946</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>566</t>
+          <t>-12.02506</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>-75.18379</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3787,32 +3787,32 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>219942</t>
+          <t>220101</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>31506 SAGRADO CORAZON DE JESUS</t>
+          <t>SAN FRANCISCO DE ASIS</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-12.07186</t>
+          <t>262</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>-75.21074</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>-12.06401</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>-75.18805</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3849,32 +3849,32 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>219956</t>
+          <t>220097</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>31507 DOMINGO F. SARMIENTO</t>
+          <t>NUESTRA SEÑORA DE COCHARCAS</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-12.06955</t>
+          <t>2143</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>-75.20631</t>
+          <t>114</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>744</t>
+          <t>-12.07517</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>-75.20169</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3911,32 +3911,32 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>224868</t>
+          <t>220064</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>30173</t>
+          <t>PILOTO SANTA ISABEL</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-12.136861</t>
+          <t>3648</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>-75.222522</t>
+          <t>209</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>-12.05843</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>-75.20263</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3973,32 +3973,32 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>640625</t>
+          <t>220035</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>CIENTIFICA</t>
+          <t>VIRGEN DE FATIMA</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-12.07373</t>
+          <t>718</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>-75.20649</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>-12.05792</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>-75.19586</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4035,37 +4035,37 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>219843</t>
+          <t>219999</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>30054 SANTA MARIA REYNA</t>
+          <t>31554 JOSE C. MARIATEGUI</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-12.070532</t>
+          <t>894</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>-75.211277</t>
+          <t>53</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>858</t>
+          <t>-12.07723</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>-75.20809</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4097,32 +4097,32 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>225636</t>
+          <t>219980</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>ANDRES BELLO</t>
+          <t>31542 VIRGEN MARIA ADMIRABLE</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-12.04342</t>
+          <t>1091</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>-75.255928</t>
+          <t>54</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>416</t>
+          <t>-12.073551</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>-75.199432</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4159,32 +4159,32 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>222906</t>
+          <t>219975</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>30209</t>
+          <t>31541 EMMA LUZMILA CALLE VERGARA</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-12.02922</t>
+          <t>1028</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>-75.22824</t>
+          <t>49</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>802</t>
+          <t>-12.06587</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>-75.20936</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4221,32 +4221,32 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>808318</t>
+          <t>219961</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>INNOVA SCHOOLS HUANCAYO</t>
+          <t>31540 SANTA ISABEL</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>-12.03791</t>
+          <t>1518</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>-75.18858</t>
+          <t>59</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>1091</t>
+          <t>-12.05764</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>-75.20275</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -4283,37 +4283,37 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>220479</t>
+          <t>219956</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>ROSA DE SANTA MARIA</t>
+          <t>31507 DOMINGO F. SARMIENTO</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>-12.073214</t>
+          <t>744</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>-75.198074</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>-12.06955</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-75.20631</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4345,32 +4345,32 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>226551</t>
+          <t>219942</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>CHINCHAYSUYO</t>
+          <t>31506 SAGRADO CORAZON DE JESUS</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>-12.1348</t>
+          <t>644</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>-75.1654</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>545</t>
+          <t>-12.07186</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>-75.21074</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4407,32 +4407,32 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>220163</t>
+          <t>219923</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>SANTA MARIA REYNA</t>
+          <t>31458 SAN JUDAS TADEO</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>-12.07529</t>
+          <t>204</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>-75.22055</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>731</t>
+          <t>-12.0676</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>-75.1937</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4469,32 +4469,32 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>219876</t>
+          <t>219904</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>30059 ROSA DE AMERICA</t>
+          <t>30128</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>-12.06955</t>
+          <t>337</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>-75.21345</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>-12.0577</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>-75.18715</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -4531,32 +4531,32 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>219975</t>
+          <t>219881</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>31541 EMMA LUZMILA CALLE VERGARA</t>
+          <t>30124 SAN FRANCISCO DE ASIS</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>-12.06587</t>
+          <t>268</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>-75.20936</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>1028</t>
+          <t>-12.06633</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>-75.19819</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4593,32 +4593,32 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>220035</t>
+          <t>219876</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>VIRGEN DE FATIMA</t>
+          <t>30059 ROSA DE AMERICA</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>-12.05792</t>
+          <t>1246</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>-75.19586</t>
+          <t>49</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>718</t>
+          <t>-12.06955</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>-75.21345</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4655,32 +4655,32 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>220832</t>
+          <t>219862</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>ZARATE</t>
+          <t>30057 / 30057 MARIA DE FATIMA</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>-12.06021</t>
+          <t>576</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>-75.20687</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>1356</t>
+          <t>-12.0761</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>-75.2133</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4717,37 +4717,37 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>219999</t>
+          <t>219857</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>31554 JOSE C. MARIATEGUI</t>
+          <t>MARIA INMACULADA</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>-12.07723</t>
+          <t>1672</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>-75.20809</t>
+          <t>121</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>-12.06567</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>-75.20904</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -4779,32 +4779,32 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>219980</t>
+          <t>219843</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>31542 VIRGEN MARIA ADMIRABLE</t>
+          <t>30054 SANTA MARIA REYNA</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>-12.073551</t>
+          <t>858</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>-75.199432</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>1091</t>
+          <t>-12.070532</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>-75.211277</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -4841,32 +4841,32 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>220177</t>
+          <t>219838</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>31363 LA ASUNCION / 406 LA ASUNCION / LA ASUNCION</t>
+          <t>30011 VIRGEN DEL CARMEN</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>-12.029846</t>
+          <t>372</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>-75.190427</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>1075</t>
+          <t>-12.06016</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>-75.194</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4903,32 +4903,32 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>223086</t>
+          <t>219824</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>31509 / 31509 RICARDO MENENDEZ MENENDEZ</t>
+          <t>30009 VIRGEN DE GUADALUPE</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>-12.0597</t>
+          <t>566</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>-75.2178</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>1144</t>
+          <t>-12.043</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>-75.1946</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4965,32 +4965,32 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>220200</t>
+          <t>219800</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>CLARETIANO</t>
+          <t>30005 SAN FRANCISCO DE ASIS / 30005 SAN FRANSISCO DE ASIS</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>-12.06242</t>
+          <t>426</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>-75.20534</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>981</t>
+          <t>-12.0338</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>-75.1909</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -5000,7 +5000,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5027,32 +5027,32 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>219961</t>
+          <t>219796</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>31540 SANTA ISABEL</t>
+          <t>30003 PEDRO R. DIAZ HUAMAN</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>-12.05764</t>
+          <t>238</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>-75.20275</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>1518</t>
+          <t>-12.02444</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>-75.18406</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -5089,32 +5089,32 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>220728</t>
+          <t>219782</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>RAMIRO VILLAVERDE LAZO</t>
+          <t>30001 SANTA ROSA DE LIMA</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>-12.05737</t>
+          <t>322</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>-75.19264</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>-12.0544</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>-75.1886</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -5151,32 +5151,32 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>220224</t>
+          <t>219777</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>ANDINO</t>
+          <t>465</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>-12.06371</t>
+          <t>280</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>-75.2065</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>795</t>
+          <t>-12.0713</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>-75.2048</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5213,32 +5213,32 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>517649</t>
+          <t>219763</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>SACO OLIVEROS</t>
+          <t>372</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>-12.05815</t>
+          <t>263</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>-75.20048</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>847</t>
+          <t>-12.0506</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>-75.199</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -5275,32 +5275,32 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>641559</t>
+          <t>219720</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>JOSE CARLOS MARIATEGUI</t>
+          <t>DANIEL ALCIDES CARRION</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>-12.07785</t>
+          <t>260</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>-75.20778</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>1324</t>
+          <t>-12.07986</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>-75.22491</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -5337,32 +5337,32 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>640461</t>
+          <t>219683</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>MANUEL COVEÑAS</t>
+          <t>30320 JESUS EL NAZARENO</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>-12.07695</t>
+          <t>476</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>-75.2098</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>-12.0736</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>-75.2241</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -5372,7 +5372,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5399,32 +5399,32 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>223246</t>
+          <t>219678</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>MARISCAL CASTILLA</t>
+          <t>300</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>-12.05916</t>
+          <t>481</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>-75.21802</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>2302</t>
+          <t>-12.073669</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>-75.199981</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -5461,42 +5461,42 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>843915</t>
+          <t>219664</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>LIDERES PACIFISTAS</t>
+          <t>254 OLIMPIA SANCHEZ MORENO</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>-12.07427</t>
+          <t>391</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>-75.21112</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>-12.06</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-75.203</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5523,32 +5523,32 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>220120</t>
+          <t>219659</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DEL ROSARIO</t>
+          <t>253</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>-12.06998</t>
+          <t>292</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>-75.21226</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>-12.07044</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>-75.21324</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">

--- a/ZonasEscolares/excels/JUNIN-HUANCAYO-HUANCAYO.xlsx
+++ b/ZonasEscolares/excels/JUNIN-HUANCAYO-HUANCAYO.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
